--- a/output/Data and Chart Outputs/ireland_gas_demand_daily.xlsx
+++ b/output/Data and Chart Outputs/ireland_gas_demand_daily.xlsx
@@ -19,9 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -61,13 +62,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -302,7 +302,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr/>
           </a:p>
@@ -340,6 +340,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -550,23 +556,65 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="300"/>
+          <min val="50"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>GWh/day</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <majorUnit val="50"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -954,6 +1002,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -996,6 +1045,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
@@ -1010,6 +1060,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
@@ -1069,7 +1120,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -1086,7 +1137,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1103,7 +1154,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1120,7 +1171,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1137,7 +1188,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1154,7 +1205,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1171,7 +1222,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1188,7 +1239,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1205,7 +1256,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1222,7 +1273,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1239,7 +1290,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1256,7 +1307,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1273,7 +1324,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1290,7 +1341,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1307,7 +1358,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1324,7 +1375,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1341,7 +1392,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1358,7 +1409,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1375,7 +1426,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1392,7 +1443,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1409,7 +1460,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1426,7 +1477,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1443,7 +1494,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1460,7 +1511,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1477,7 +1528,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1494,7 +1545,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1511,7 +1562,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1528,7 +1579,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1545,7 +1596,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1562,7 +1613,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1579,7 +1630,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1596,7 +1647,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1613,7 +1664,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1630,7 +1681,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1647,7 +1698,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1664,7 +1715,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1681,7 +1732,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -1698,7 +1749,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -1715,7 +1766,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -1732,7 +1783,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -1749,7 +1800,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -1766,7 +1817,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -1783,7 +1834,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -1800,7 +1851,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -1817,7 +1868,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -1834,7 +1885,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -1851,7 +1902,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -1868,7 +1919,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -1885,7 +1936,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -1902,7 +1953,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -1919,7 +1970,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -1936,7 +1987,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -1953,7 +2004,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -1970,7 +2021,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -1987,7 +2038,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2004,7 +2055,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2021,7 +2072,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2038,7 +2089,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2055,7 +2106,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2072,7 +2123,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2089,7 +2140,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2106,7 +2157,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2123,7 +2174,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">

--- a/output/Data and Chart Outputs/ireland_gas_demand_daily.xlsx
+++ b/output/Data and Chart Outputs/ireland_gas_demand_daily.xlsx
@@ -156,6 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Ireland gas demand by sector (monthly average) (to Mar/26)</a:t>
             </a:r>
           </a:p>
@@ -375,6 +376,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Ireland total gas demand - water year (Oct-Sep), data to 2026-03-31</a:t>
             </a:r>
           </a:p>
@@ -487,7 +489,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1127,7 +1129,7 @@
         <v>101.6475359032258</v>
       </c>
       <c r="C2" t="n">
-        <v>14.01733619354839</v>
+        <v>14.01733619354838</v>
       </c>
       <c r="D2" t="n">
         <v>10.98894564516129</v>
@@ -1150,7 +1152,7 @@
         <v>11.08289353571429</v>
       </c>
       <c r="E3" t="n">
-        <v>55.93197810714286</v>
+        <v>55.93197810714287</v>
       </c>
     </row>
     <row r="4">
@@ -1192,7 +1194,7 @@
         <v>44317</v>
       </c>
       <c r="B6" t="n">
-        <v>77.52555548387096</v>
+        <v>77.52555548387097</v>
       </c>
       <c r="C6" t="n">
         <v>20.2856264516129</v>
@@ -1209,13 +1211,13 @@
         <v>44348</v>
       </c>
       <c r="B7" t="n">
-        <v>93.34429626666666</v>
+        <v>93.34429626666665</v>
       </c>
       <c r="C7" t="n">
         <v>19.40885733333333</v>
       </c>
       <c r="D7" t="n">
-        <v>7.872190966666667</v>
+        <v>7.872190966666666</v>
       </c>
       <c r="E7" t="n">
         <v>12.39220126666667</v>
@@ -1232,7 +1234,7 @@
         <v>17.22772229032258</v>
       </c>
       <c r="D8" t="n">
-        <v>7.117079161290323</v>
+        <v>7.117079161290321</v>
       </c>
       <c r="E8" t="n">
         <v>9.684117483870969</v>
@@ -1243,13 +1245,13 @@
         <v>44409</v>
       </c>
       <c r="B9" t="n">
-        <v>99.97292132258065</v>
+        <v>99.97292132258063</v>
       </c>
       <c r="C9" t="n">
         <v>17.122023</v>
       </c>
       <c r="D9" t="n">
-        <v>7.538296548387097</v>
+        <v>7.538296548387098</v>
       </c>
       <c r="E9" t="n">
         <v>11.35396164516129</v>
@@ -1260,7 +1262,7 @@
         <v>44440</v>
       </c>
       <c r="B10" t="n">
-        <v>94.58271296666666</v>
+        <v>94.58271296666665</v>
       </c>
       <c r="C10" t="n">
         <v>17.21619426666667</v>
@@ -1277,13 +1279,13 @@
         <v>44470</v>
       </c>
       <c r="B11" t="n">
-        <v>82.18047332258065</v>
+        <v>82.18047332258067</v>
       </c>
       <c r="C11" t="n">
         <v>15.59452877419355</v>
       </c>
       <c r="D11" t="n">
-        <v>8.911756064516128</v>
+        <v>8.91175606451613</v>
       </c>
       <c r="E11" t="n">
         <v>25.85183358064516</v>
@@ -1311,7 +1313,7 @@
         <v>44531</v>
       </c>
       <c r="B13" t="n">
-        <v>85.96813612903226</v>
+        <v>85.96813612903227</v>
       </c>
       <c r="C13" t="n">
         <v>11.92138467741936</v>
@@ -1320,7 +1322,7 @@
         <v>10.04711016129032</v>
       </c>
       <c r="E13" t="n">
-        <v>51.62712761290322</v>
+        <v>51.62712761290323</v>
       </c>
     </row>
     <row r="14">
@@ -1337,7 +1339,7 @@
         <v>10.7739704516129</v>
       </c>
       <c r="E14" t="n">
-        <v>54.94668564516129</v>
+        <v>54.9466856451613</v>
       </c>
     </row>
     <row r="15">
@@ -1354,7 +1356,7 @@
         <v>11.14241589285714</v>
       </c>
       <c r="E15" t="n">
-        <v>53.05841482142857</v>
+        <v>53.05841482142858</v>
       </c>
     </row>
     <row r="16">
@@ -1362,7 +1364,7 @@
         <v>44621</v>
       </c>
       <c r="B16" t="n">
-        <v>89.15928132258064</v>
+        <v>89.15928132258065</v>
       </c>
       <c r="C16" t="n">
         <v>17.05767674193548</v>
@@ -1371,7 +1373,7 @@
         <v>10.8050335483871</v>
       </c>
       <c r="E16" t="n">
-        <v>42.8979049032258</v>
+        <v>42.89790490322581</v>
       </c>
     </row>
     <row r="17">
@@ -1402,7 +1404,7 @@
         <v>18.56680612903225</v>
       </c>
       <c r="D18" t="n">
-        <v>8.989473709677419</v>
+        <v>8.989473709677421</v>
       </c>
       <c r="E18" t="n">
         <v>17.89008593548387</v>
@@ -1419,7 +1421,7 @@
         <v>18.09099853333333</v>
       </c>
       <c r="D19" t="n">
-        <v>8.5418387</v>
+        <v>8.541838700000001</v>
       </c>
       <c r="E19" t="n">
         <v>13.09462843333333</v>
@@ -1430,7 +1432,7 @@
         <v>44743</v>
       </c>
       <c r="B20" t="n">
-        <v>116.1250032258064</v>
+        <v>116.1250032258065</v>
       </c>
       <c r="C20" t="n">
         <v>16.46444561290323</v>
@@ -1439,7 +1441,7 @@
         <v>7.174252258064516</v>
       </c>
       <c r="E20" t="n">
-        <v>9.324541870967741</v>
+        <v>9.324541870967742</v>
       </c>
     </row>
     <row r="21">
@@ -1453,7 +1455,7 @@
         <v>15.80868680645161</v>
       </c>
       <c r="D21" t="n">
-        <v>7.408554451612903</v>
+        <v>7.408554451612902</v>
       </c>
       <c r="E21" t="n">
         <v>8.920926225806452</v>
@@ -1470,7 +1472,7 @@
         <v>15.5816121</v>
       </c>
       <c r="D22" t="n">
-        <v>7.791731400000001</v>
+        <v>7.7917314</v>
       </c>
       <c r="E22" t="n">
         <v>13.567521</v>
@@ -1487,7 +1489,7 @@
         <v>15.56913648387097</v>
       </c>
       <c r="D23" t="n">
-        <v>8.360097967741936</v>
+        <v>8.360097967741932</v>
       </c>
       <c r="E23" t="n">
         <v>22.09579061290323</v>
@@ -1504,10 +1506,10 @@
         <v>15.4293463</v>
       </c>
       <c r="D24" t="n">
-        <v>9.645737266666666</v>
+        <v>9.645737266666668</v>
       </c>
       <c r="E24" t="n">
-        <v>36.02208196666666</v>
+        <v>36.02208196666667</v>
       </c>
     </row>
     <row r="25">
@@ -1541,7 +1543,7 @@
         <v>10.38196116129032</v>
       </c>
       <c r="E26" t="n">
-        <v>50.96684364516129</v>
+        <v>50.96684364516128</v>
       </c>
     </row>
     <row r="27">
@@ -1549,7 +1551,7 @@
         <v>44958</v>
       </c>
       <c r="B27" t="n">
-        <v>96.34910728571428</v>
+        <v>96.34910728571431</v>
       </c>
       <c r="C27" t="n">
         <v>14.04376675</v>
@@ -1558,7 +1560,7 @@
         <v>10.28443967857143</v>
       </c>
       <c r="E27" t="n">
-        <v>42.83185985714285</v>
+        <v>42.83185985714287</v>
       </c>
     </row>
     <row r="28">
@@ -1566,7 +1568,7 @@
         <v>44986</v>
       </c>
       <c r="B28" t="n">
-        <v>97.91715032258065</v>
+        <v>97.91715032258064</v>
       </c>
       <c r="C28" t="n">
         <v>16.69086270967742</v>
@@ -1589,7 +1591,7 @@
         <v>17.21928606666667</v>
       </c>
       <c r="D29" t="n">
-        <v>9.752577533333334</v>
+        <v>9.752577533333332</v>
       </c>
       <c r="E29" t="n">
         <v>29.03862843333333</v>
@@ -1600,13 +1602,13 @@
         <v>45047</v>
       </c>
       <c r="B30" t="n">
-        <v>104.1962294193548</v>
+        <v>104.1962294193549</v>
       </c>
       <c r="C30" t="n">
         <v>16.94012112903226</v>
       </c>
       <c r="D30" t="n">
-        <v>8.333989193548387</v>
+        <v>8.333989193548389</v>
       </c>
       <c r="E30" t="n">
         <v>14.73898896774194</v>
@@ -1623,7 +1625,7 @@
         <v>15.884088</v>
       </c>
       <c r="D31" t="n">
-        <v>7.252935066666667</v>
+        <v>7.252935066666666</v>
       </c>
       <c r="E31" t="n">
         <v>9.159117233333335</v>
@@ -1637,7 +1639,7 @@
         <v>90.28327954838709</v>
       </c>
       <c r="C32" t="n">
-        <v>15.17739361290323</v>
+        <v>15.17739361290322</v>
       </c>
       <c r="D32" t="n">
         <v>7.018810935483871</v>
@@ -1651,7 +1653,7 @@
         <v>45139</v>
       </c>
       <c r="B33" t="n">
-        <v>87.58609293548388</v>
+        <v>87.58609293548386</v>
       </c>
       <c r="C33" t="n">
         <v>15.58031864516129</v>
@@ -1674,7 +1676,7 @@
         <v>15.50727336666667</v>
       </c>
       <c r="D34" t="n">
-        <v>7.515897533333333</v>
+        <v>7.515897533333334</v>
       </c>
       <c r="E34" t="n">
         <v>12.46071276666667</v>
@@ -1685,7 +1687,7 @@
         <v>45200</v>
       </c>
       <c r="B35" t="n">
-        <v>88.34066287096773</v>
+        <v>88.34066287096775</v>
       </c>
       <c r="C35" t="n">
         <v>14.89583464516129</v>
@@ -1702,13 +1704,13 @@
         <v>45231</v>
       </c>
       <c r="B36" t="n">
-        <v>91.25343509999999</v>
+        <v>91.2534351</v>
       </c>
       <c r="C36" t="n">
         <v>14.18755036666667</v>
       </c>
       <c r="D36" t="n">
-        <v>9.969979800000001</v>
+        <v>9.969979800000003</v>
       </c>
       <c r="E36" t="n">
         <v>39.90380466666667</v>
@@ -1719,7 +1721,7 @@
         <v>45261</v>
       </c>
       <c r="B37" t="n">
-        <v>73.77021745161291</v>
+        <v>73.77021745161292</v>
       </c>
       <c r="C37" t="n">
         <v>11.34918377419355</v>
@@ -1728,7 +1730,7 @@
         <v>9.233186064516129</v>
       </c>
       <c r="E37" t="n">
-        <v>44.63626219354839</v>
+        <v>44.6362621935484</v>
       </c>
     </row>
     <row r="38">
@@ -1753,7 +1755,7 @@
         <v>45323</v>
       </c>
       <c r="B39" t="n">
-        <v>84.58371637931035</v>
+        <v>84.58371637931036</v>
       </c>
       <c r="C39" t="n">
         <v>13.98243431034483</v>
@@ -1770,7 +1772,7 @@
         <v>45352</v>
       </c>
       <c r="B40" t="n">
-        <v>83.06132606451612</v>
+        <v>83.06132606451611</v>
       </c>
       <c r="C40" t="n">
         <v>16.72012909677419</v>
@@ -1779,7 +1781,7 @@
         <v>9.995179838709678</v>
       </c>
       <c r="E40" t="n">
-        <v>40.53583051612903</v>
+        <v>40.53583051612902</v>
       </c>
     </row>
     <row r="41">
@@ -1787,7 +1789,7 @@
         <v>45383</v>
       </c>
       <c r="B41" t="n">
-        <v>87.3965726</v>
+        <v>87.39657259999998</v>
       </c>
       <c r="C41" t="n">
         <v>16.44545913333333</v>
@@ -1796,7 +1798,7 @@
         <v>9.381534566666666</v>
       </c>
       <c r="E41" t="n">
-        <v>30.97515066666666</v>
+        <v>30.97515066666667</v>
       </c>
     </row>
     <row r="42">
@@ -1807,7 +1809,7 @@
         <v>101.7222222258064</v>
       </c>
       <c r="C42" t="n">
-        <v>16.52875125806452</v>
+        <v>16.52875125806451</v>
       </c>
       <c r="D42" t="n">
         <v>8.350922741935484</v>
@@ -1821,7 +1823,7 @@
         <v>45444</v>
       </c>
       <c r="B43" t="n">
-        <v>87.03690920000001</v>
+        <v>87.0369092</v>
       </c>
       <c r="C43" t="n">
         <v>15.69382</v>
@@ -1838,13 +1840,13 @@
         <v>45474</v>
       </c>
       <c r="B44" t="n">
-        <v>93.3682258064516</v>
+        <v>93.36822580645159</v>
       </c>
       <c r="C44" t="n">
         <v>14.65752758064516</v>
       </c>
       <c r="D44" t="n">
-        <v>7.869879129032258</v>
+        <v>7.86987912903226</v>
       </c>
       <c r="E44" t="n">
         <v>10.29948238709677</v>
@@ -1864,7 +1866,7 @@
         <v>7.791889806451613</v>
       </c>
       <c r="E45" t="n">
-        <v>9.519965354838709</v>
+        <v>9.51996535483871</v>
       </c>
     </row>
     <row r="46">
@@ -1872,7 +1874,7 @@
         <v>45536</v>
       </c>
       <c r="B46" t="n">
-        <v>94.05997003333333</v>
+        <v>94.05997003333331</v>
       </c>
       <c r="C46" t="n">
         <v>16.1190598</v>
@@ -1881,7 +1883,7 @@
         <v>9.010508933333334</v>
       </c>
       <c r="E46" t="n">
-        <v>15.94720086666667</v>
+        <v>15.94720086666666</v>
       </c>
     </row>
     <row r="47">
@@ -1895,10 +1897,10 @@
         <v>14.47556906451613</v>
       </c>
       <c r="D47" t="n">
-        <v>9.678657064516129</v>
+        <v>9.678657064516127</v>
       </c>
       <c r="E47" t="n">
-        <v>24.90079338709677</v>
+        <v>24.90079338709678</v>
       </c>
     </row>
     <row r="48">
@@ -1912,10 +1914,10 @@
         <v>15.3063712</v>
       </c>
       <c r="D48" t="n">
-        <v>9.942685233333332</v>
+        <v>9.942685233333334</v>
       </c>
       <c r="E48" t="n">
-        <v>38.1590492</v>
+        <v>38.15904920000001</v>
       </c>
     </row>
     <row r="49">
@@ -1923,13 +1925,13 @@
         <v>45627</v>
       </c>
       <c r="B49" t="n">
-        <v>94.12673212903226</v>
+        <v>94.12673212903229</v>
       </c>
       <c r="C49" t="n">
-        <v>12.19396161290323</v>
+        <v>12.19396161290322</v>
       </c>
       <c r="D49" t="n">
-        <v>9.440492000000001</v>
+        <v>9.440491999999999</v>
       </c>
       <c r="E49" t="n">
         <v>45.05231545161291</v>
@@ -1957,7 +1959,7 @@
         <v>45689</v>
       </c>
       <c r="B51" t="n">
-        <v>79.84054174999999</v>
+        <v>79.84054175000001</v>
       </c>
       <c r="C51" t="n">
         <v>14.30371853571429</v>
@@ -1974,7 +1976,7 @@
         <v>45717</v>
       </c>
       <c r="B52" t="n">
-        <v>93.7443100967742</v>
+        <v>93.74431009677423</v>
       </c>
       <c r="C52" t="n">
         <v>16.58905164516129</v>
@@ -1983,7 +1985,7 @@
         <v>10.23537287096774</v>
       </c>
       <c r="E52" t="n">
-        <v>35.90932380645161</v>
+        <v>35.9093238064516</v>
       </c>
     </row>
     <row r="53">
@@ -1991,7 +1993,7 @@
         <v>45748</v>
       </c>
       <c r="B53" t="n">
-        <v>92.53192713333333</v>
+        <v>92.53192713333334</v>
       </c>
       <c r="C53" t="n">
         <v>16.748552</v>
@@ -2025,13 +2027,13 @@
         <v>45809</v>
       </c>
       <c r="B55" t="n">
-        <v>80.1331852</v>
+        <v>80.13318520000001</v>
       </c>
       <c r="C55" t="n">
         <v>16.5369571</v>
       </c>
       <c r="D55" t="n">
-        <v>7.572935933333333</v>
+        <v>7.572935933333334</v>
       </c>
       <c r="E55" t="n">
         <v>10.7918119</v>
@@ -2065,10 +2067,10 @@
         <v>15.64460070967742</v>
       </c>
       <c r="D57" t="n">
-        <v>6.829170548387096</v>
+        <v>6.829170548387095</v>
       </c>
       <c r="E57" t="n">
-        <v>8.572429064516129</v>
+        <v>8.572429064516131</v>
       </c>
     </row>
     <row r="58">
@@ -2076,7 +2078,7 @@
         <v>45901</v>
       </c>
       <c r="B58" t="n">
-        <v>83.06975793333332</v>
+        <v>83.06975793333335</v>
       </c>
       <c r="C58" t="n">
         <v>16.82295636666667</v>
@@ -2093,13 +2095,13 @@
         <v>45931</v>
       </c>
       <c r="B59" t="n">
-        <v>90.93646674193548</v>
+        <v>90.9364667419355</v>
       </c>
       <c r="C59" t="n">
         <v>16.24527212903226</v>
       </c>
       <c r="D59" t="n">
-        <v>8.393120612903225</v>
+        <v>8.393120612903227</v>
       </c>
       <c r="E59" t="n">
         <v>25.81541935483871</v>
@@ -2116,7 +2118,7 @@
         <v>16.3061647</v>
       </c>
       <c r="D60" t="n">
-        <v>9.563587099999999</v>
+        <v>9.563587099999998</v>
       </c>
       <c r="E60" t="n">
         <v>38.88018539999999</v>
@@ -2136,7 +2138,7 @@
         <v>9.252046967741935</v>
       </c>
       <c r="E61" t="n">
-        <v>44.87465558064516</v>
+        <v>44.87465558064517</v>
       </c>
     </row>
     <row r="62">
@@ -2144,7 +2146,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>112.7563396774194</v>
+        <v>112.7563396774193</v>
       </c>
       <c r="C62" t="n">
         <v>12.96139774193548</v>
@@ -2184,10 +2186,10 @@
         <v>16.17501870967742</v>
       </c>
       <c r="D64" t="n">
-        <v>10.18003067741936</v>
+        <v>10.18003067741935</v>
       </c>
       <c r="E64" t="n">
-        <v>37.9446876451613</v>
+        <v>37.94468764516128</v>
       </c>
     </row>
   </sheetData>
@@ -13936,7 +13938,7 @@
         <v>133.066389</v>
       </c>
       <c r="F151" t="n">
-        <v>170.0233349999999</v>
+        <v>170.023335</v>
       </c>
     </row>
     <row r="152">
@@ -18036,7 +18038,7 @@
         <v>91.088334</v>
       </c>
       <c r="F356" t="n">
-        <v>166.6883680000001</v>
+        <v>166.688368</v>
       </c>
     </row>
     <row r="357">
@@ -29976,7 +29978,7 @@
         <v>140.939745</v>
       </c>
       <c r="F953" t="n">
-        <v>170.7960069999999</v>
+        <v>170.796007</v>
       </c>
     </row>
     <row r="954">
@@ -44436,7 +44438,7 @@
         <v>67.26194599999999</v>
       </c>
       <c r="F1676" t="n">
-        <v>98.134056</v>
+        <v>98.13405599999999</v>
       </c>
     </row>
     <row r="1677">
@@ -45096,7 +45098,7 @@
         <v>63.988333</v>
       </c>
       <c r="F1709" t="n">
-        <v>94.42001500000001</v>
+        <v>94.42001499999999</v>
       </c>
     </row>
     <row r="1710">
@@ -49436,7 +49438,7 @@
         <v>43.281668</v>
       </c>
       <c r="F1926" t="n">
-        <v>92.944003</v>
+        <v>92.94400300000001</v>
       </c>
     </row>
     <row r="1927">
@@ -51396,7 +51398,7 @@
         <v>69.008612</v>
       </c>
       <c r="F2024" t="n">
-        <v>99.152539</v>
+        <v>99.15253899999999</v>
       </c>
     </row>
     <row r="2025">
@@ -51796,7 +51798,7 @@
         <v>63.032778</v>
       </c>
       <c r="F2044" t="n">
-        <v>94.46542100000001</v>
+        <v>94.46542099999999</v>
       </c>
     </row>
     <row r="2045">
@@ -52236,7 +52238,7 @@
         <v>62.767777</v>
       </c>
       <c r="F2066" t="n">
-        <v>95.12891399999999</v>
+        <v>95.12891400000001</v>
       </c>
     </row>
     <row r="2067">
@@ -52636,7 +52638,7 @@
         <v>62.378333</v>
       </c>
       <c r="F2086" t="n">
-        <v>99.923895</v>
+        <v>99.92389499999999</v>
       </c>
     </row>
     <row r="2087">
@@ -52916,7 +52918,7 @@
         <v>53.933333</v>
       </c>
       <c r="F2100" t="n">
-        <v>94.103011</v>
+        <v>94.10301100000001</v>
       </c>
     </row>
     <row r="2101">
@@ -54456,7 +54458,7 @@
         <v>40.698888</v>
       </c>
       <c r="F2177" t="n">
-        <v>97.788008</v>
+        <v>97.78800799999999</v>
       </c>
     </row>
     <row r="2178">
@@ -55776,7 +55778,7 @@
         <v>81.305554</v>
       </c>
       <c r="F2243" t="n">
-        <v>145.9962750000001</v>
+        <v>145.996275</v>
       </c>
     </row>
     <row r="2244">
@@ -56676,7 +56678,7 @@
         <v>39.793333</v>
       </c>
       <c r="F2288" t="n">
-        <v>96.522767</v>
+        <v>96.52276699999999</v>
       </c>
     </row>
     <row r="2289">
@@ -56716,7 +56718,7 @@
         <v>50.045233</v>
       </c>
       <c r="F2290" t="n">
-        <v>99.010476</v>
+        <v>99.01047600000001</v>
       </c>
     </row>
     <row r="2291">
@@ -56836,7 +56838,7 @@
         <v>45.9275</v>
       </c>
       <c r="F2296" t="n">
-        <v>93.25813100000001</v>
+        <v>93.25813099999999</v>
       </c>
     </row>
     <row r="2297">
@@ -56856,7 +56858,7 @@
         <v>44.02861</v>
       </c>
       <c r="F2297" t="n">
-        <v>98.41323300000001</v>
+        <v>98.41323299999999</v>
       </c>
     </row>
     <row r="2298">
@@ -59236,7 +59238,7 @@
         <v>72.42833299999999</v>
       </c>
       <c r="F2416" t="n">
-        <v>97.82299500000001</v>
+        <v>97.82299499999999</v>
       </c>
     </row>
     <row r="2417">
@@ -59836,7 +59838,7 @@
         <v>55.169446</v>
       </c>
       <c r="F2446" t="n">
-        <v>95.86259800000001</v>
+        <v>95.86259799999999</v>
       </c>
     </row>
     <row r="2447">
@@ -61816,7 +61818,7 @@
         <v>105.680833</v>
       </c>
       <c r="F2545" t="n">
-        <v>170.1250800000001</v>
+        <v>170.12508</v>
       </c>
     </row>
     <row r="2546">
@@ -62536,7 +62538,7 @@
         <v>77.520832</v>
       </c>
       <c r="F2581" t="n">
-        <v>152.3945749999999</v>
+        <v>152.394575</v>
       </c>
     </row>
     <row r="2582">
@@ -62616,7 +62618,7 @@
         <v>114.07222</v>
       </c>
       <c r="F2585" t="n">
-        <v>189.2807670000001</v>
+        <v>189.280767</v>
       </c>
     </row>
     <row r="2586">
@@ -63256,7 +63258,7 @@
         <v>100.719444</v>
       </c>
       <c r="F2617" t="n">
-        <v>176.7435709999999</v>
+        <v>176.743571</v>
       </c>
     </row>
     <row r="2618">
@@ -67076,7 +67078,7 @@
         <v>59.512223</v>
       </c>
       <c r="F2808" t="n">
-        <v>91.061772</v>
+        <v>91.06177199999999</v>
       </c>
     </row>
     <row r="2809">
@@ -67156,7 +67158,7 @@
         <v>50.614722</v>
       </c>
       <c r="F2812" t="n">
-        <v>91.152081</v>
+        <v>91.15208100000001</v>
       </c>
     </row>
     <row r="2813">
@@ -67236,7 +67238,7 @@
         <v>54.925834</v>
       </c>
       <c r="F2816" t="n">
-        <v>96.23254799999999</v>
+        <v>96.23254800000001</v>
       </c>
     </row>
     <row r="2817">
